--- a/temp_recipe.xlsx
+++ b/temp_recipe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Unity_Project\Team_one_cubed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A248FD4-C3C4-4FF3-A8E3-E0162D2586B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6FBDC9D-88A9-4307-81E4-6872362342DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{135C58CC-9C3A-49AD-BD19-1CDA1F882F74}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{135C58CC-9C3A-49AD-BD19-1CDA1F882F74}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="10">
   <si>
     <t>아이스티</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -74,6 +74,10 @@
   </si>
   <si>
     <t>얼음물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>에스프레소</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -458,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB829040-A438-4646-AA8B-8CCD0896E6E9}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.5" customWidth="1"/>
@@ -534,6 +538,14 @@
         <v>4</v>
       </c>
     </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/temp_recipe.xlsx
+++ b/temp_recipe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Unity_Project\Team_one_cubed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6FBDC9D-88A9-4307-81E4-6872362342DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D52759B-EF9D-481E-A787-6707D8E38190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{135C58CC-9C3A-49AD-BD19-1CDA1F882F74}"/>
+    <workbookView xWindow="7095" yWindow="2295" windowWidth="21600" windowHeight="11295" xr2:uid="{135C58CC-9C3A-49AD-BD19-1CDA1F882F74}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,15 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="10">
-  <si>
-    <t>아이스티</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아이스아메리카노</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="9">
   <si>
     <t>아메리카노</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -77,7 +69,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>에스프레소</t>
+    <t>아이스 아메리카노</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>복숭아 아이스티</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -462,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB829040-A438-4646-AA8B-8CCD0896E6E9}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.5" customWidth="1"/>
@@ -473,77 +469,69 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
         <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
         <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
         <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" t="s">
         <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
